--- a/Mod_Korean/Lang/KR/Dialog/Drama/fiama.xlsx
+++ b/Mod_Korean/Lang/KR/Dialog/Drama/fiama.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="214">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -382,20 +382,16 @@
     <t xml:space="preserve">firstDream</t>
   </si>
   <si>
-    <t xml:space="preserve">私の夢を見た？</t>
+    <t xml:space="preserve">n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">giveStoryBook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あら、#pc_name#。</t>
   </si>
   <si>
     <t xml:space="preserve">I wish you would die.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…そう、よほどひどく頭を打ったのね。まずはしっかり休養をとるためにもベッドを作ってみたらどう？
-眠い時に「瞑想」を行うことでも睡眠はとれるけど、ベッドを使えばいつでも休むことができるし、疲労回復の効果も高いのよ。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">giveStoryBook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あら、#pc_name#。</t>
   </si>
   <si>
     <t xml:space="preserve">そう、まだ奇妙な夢を見ているのね。
@@ -1293,7 +1289,7 @@
         <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" ht="12.8">
@@ -1310,7 +1306,7 @@
         <v>23</v>
       </c>
       <c r="K13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" ht="12.8">
@@ -1333,7 +1329,7 @@
         <v>28</v>
       </c>
       <c r="K16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" ht="12.8">
@@ -1356,7 +1352,7 @@
         <v>32</v>
       </c>
       <c r="K17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" ht="12.8">
@@ -1376,7 +1372,7 @@
         <v>35</v>
       </c>
       <c r="K18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" ht="12.8">
@@ -1429,7 +1425,7 @@
         <v>44</v>
       </c>
       <c r="K26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" ht="12.8">
@@ -1449,7 +1445,7 @@
         <v>47</v>
       </c>
       <c r="K27" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" ht="12.8">
@@ -1469,7 +1465,7 @@
         <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" ht="12.8">
@@ -1489,7 +1485,7 @@
         <v>53</v>
       </c>
       <c r="K29" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" ht="12.8">
@@ -1509,7 +1505,7 @@
         <v>56</v>
       </c>
       <c r="K30" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" ht="12.8">
@@ -1592,7 +1588,7 @@
         <v>64</v>
       </c>
       <c r="K43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" ht="12.8">
@@ -1619,7 +1615,7 @@
         <v>67</v>
       </c>
       <c r="K47" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" ht="12.8">
@@ -1651,7 +1647,7 @@
         <v>71</v>
       </c>
       <c r="K51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" ht="12.8">
@@ -1675,7 +1671,7 @@
         <v>74</v>
       </c>
       <c r="K56" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="57" ht="85.05">
@@ -1689,7 +1685,7 @@
         <v>76</v>
       </c>
       <c r="K57" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" ht="64.15">
@@ -1703,7 +1699,7 @@
         <v>78</v>
       </c>
       <c r="K58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" ht="12.8">
@@ -1725,7 +1721,7 @@
         <v>80</v>
       </c>
       <c r="K61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" ht="12.8">
@@ -1745,7 +1741,7 @@
         <v>83</v>
       </c>
       <c r="K62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" ht="12.8">
@@ -1768,7 +1764,7 @@
         <v>87</v>
       </c>
       <c r="K63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="64" ht="12.8">
@@ -1791,7 +1787,7 @@
         <v>90</v>
       </c>
       <c r="K64" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" ht="12.8">
@@ -1811,7 +1807,7 @@
         <v>92</v>
       </c>
       <c r="K65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" ht="12.8">
@@ -1838,7 +1834,7 @@
         <v>94</v>
       </c>
       <c r="K70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="71" ht="12.8">
@@ -1863,7 +1859,7 @@
         <v>98</v>
       </c>
       <c r="K74" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="79" ht="12.8">
@@ -1882,7 +1878,7 @@
         <v>100</v>
       </c>
       <c r="K80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" ht="12.8">
@@ -1906,7 +1902,7 @@
         <v>102</v>
       </c>
       <c r="K84" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" ht="85.05">
@@ -1920,7 +1916,7 @@
         <v>104</v>
       </c>
       <c r="K85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="86" ht="12.8">
@@ -1948,7 +1944,7 @@
         <v>108</v>
       </c>
       <c r="K87" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="88" ht="12.8">
@@ -1969,21 +1965,24 @@
         <v>110</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K91" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="92" ht="74.6">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="92" ht="12.8">
       <c r="H92" s="1">
         <v>28</v>
       </c>
-      <c r="I92" s="4" t="s">
-        <v>112</v>
+      <c r="I92" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="K92" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="93" ht="12.8">
@@ -1993,7 +1992,7 @@
     </row>
     <row r="96" ht="12.8">
       <c r="A96" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="97" ht="12.8">
@@ -2001,13 +2000,13 @@
         <v>29</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K97" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" ht="95.5">
@@ -2015,10 +2014,10 @@
         <v>30</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K98" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="99" ht="12.8">
@@ -2028,7 +2027,7 @@
     </row>
     <row r="101" ht="12.8">
       <c r="A101" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" ht="113.4">
@@ -2036,13 +2035,13 @@
         <v>31</v>
       </c>
       <c r="I102" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J102" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="J102" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="K102" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="103" ht="79.85">
@@ -2050,21 +2049,21 @@
         <v>33</v>
       </c>
       <c r="I103" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J103" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="J103" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="K103" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="104" ht="12.8">
       <c r="D104" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="105" ht="12.8">
@@ -2074,7 +2073,7 @@
     </row>
     <row r="108" ht="12.8">
       <c r="A108" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="109" ht="91">
@@ -2082,18 +2081,18 @@
         <v>32</v>
       </c>
       <c r="I109" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J109" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="J109" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="K109" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="111" ht="12.8">
       <c r="D111" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" ht="12.8">
@@ -2103,15 +2102,15 @@
     </row>
     <row r="115" ht="12.8">
       <c r="A115" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="116" ht="12.8">
       <c r="D116" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="117" ht="13.8">
@@ -2120,13 +2119,13 @@
         <v>34</v>
       </c>
       <c r="I117" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="J117" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="J117" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="K117" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="118" ht="79.85">
@@ -2134,13 +2133,13 @@
         <v>35</v>
       </c>
       <c r="I118" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="J118" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="J118" s="4" t="s">
-        <v>132</v>
-      </c>
       <c r="K118" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="119" ht="46.25">
@@ -2148,18 +2147,18 @@
         <v>36</v>
       </c>
       <c r="I119" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="J119" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="J119" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="K119" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="120" ht="12.8">
       <c r="D120" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" ht="12.8">
@@ -2169,7 +2168,7 @@
     </row>
     <row r="124" ht="12.8">
       <c r="A124" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" ht="12.8">
@@ -2181,21 +2180,21 @@
         <v>37</v>
       </c>
       <c r="I126" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J126" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="J126" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="K126" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="127" ht="12.8">
       <c r="D127" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="128" ht="12.8">
@@ -2205,7 +2204,7 @@
     </row>
     <row r="130" ht="12.8">
       <c r="A130" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="131" ht="12.8">
@@ -2217,13 +2216,13 @@
         <v>38</v>
       </c>
       <c r="I132" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="J132" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="J132" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="K132" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="133" ht="35.05">
@@ -2231,18 +2230,18 @@
         <v>39</v>
       </c>
       <c r="I133" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="J133" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="J133" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="K133" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="134" ht="12.8">
       <c r="D134" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="135" ht="12.8">
@@ -2252,15 +2251,15 @@
     </row>
     <row r="140" ht="12.8">
       <c r="A140" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="142" ht="12.8">
       <c r="D142" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="145" ht="57.45">
@@ -2268,13 +2267,13 @@
         <v>41</v>
       </c>
       <c r="I145" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J145" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="J145" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="K145" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="146" ht="68.65">
@@ -2282,18 +2281,18 @@
         <v>42</v>
       </c>
       <c r="I146" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="J146" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="J146" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="K146" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="147" ht="13.8">
       <c r="A147" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>26</v>
@@ -2302,18 +2301,18 @@
         <v>43</v>
       </c>
       <c r="I147" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="J147" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="J147" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="K147" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="148" ht="13.8">
       <c r="A148" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>26</v>
@@ -2322,18 +2321,18 @@
         <v>44</v>
       </c>
       <c r="I148" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="J148" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="J148" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="K148" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="149" ht="13.8">
       <c r="A149" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>26</v>
@@ -2342,18 +2341,18 @@
         <v>45</v>
       </c>
       <c r="I149" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="J149" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="J149" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="K149" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="150" ht="13.8">
       <c r="A150" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>26</v>
@@ -2363,18 +2362,18 @@
         <v>46</v>
       </c>
       <c r="I150" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="J150" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J150" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="K150" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="151" ht="13.8">
       <c r="A151" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>26</v>
@@ -2383,18 +2382,18 @@
         <v>47</v>
       </c>
       <c r="I151" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="J151" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="J151" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="K151" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="152" ht="13.8">
       <c r="A152" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>26</v>
@@ -2403,13 +2402,13 @@
         <v>48</v>
       </c>
       <c r="I152" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J152" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J152" s="4" t="s">
-        <v>162</v>
-      </c>
       <c r="K152" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="153" ht="13.8">
@@ -2418,7 +2417,7 @@
     </row>
     <row r="154" ht="12.8">
       <c r="A154" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I154" s="4"/>
     </row>
@@ -2430,13 +2429,13 @@
         <v>49</v>
       </c>
       <c r="I156" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J156" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J156" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="K156" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="157" ht="12.8">
@@ -2444,12 +2443,12 @@
         <v>57</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="158" ht="12.8">
       <c r="D158" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="159" ht="12.8">
